--- a/output/pdf_financials_xlsx/ECCF.P.xlsx
+++ b/output/pdf_financials_xlsx/ECCF.P.xlsx
@@ -2496,19 +2496,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.065233</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.065233</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.065233</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.065233</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.065233</v>
       </c>
     </row>
     <row r="93">
@@ -3828,7 +3828,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -4066,7 +4070,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>0.065233</v>
       </c>
@@ -4298,7 +4306,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>0.065233</v>
       </c>

--- a/output/pdf_financials_xlsx/ECCF.P.xlsx
+++ b/output/pdf_financials_xlsx/ECCF.P.xlsx
@@ -1180,19 +1180,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.340962</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.280929</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.219724</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.03999</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.001351</v>
       </c>
     </row>
     <row r="35">
@@ -1224,19 +1224,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.340962</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.280929</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.219724</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.03999</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.001351</v>
       </c>
     </row>
     <row r="37">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/ECCF.P.xlsx
+++ b/output/pdf_financials_xlsx/ECCF.P.xlsx
@@ -2679,19 +2679,19 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003583</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002514</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002808</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.008758</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.017663</v>
       </c>
     </row>
     <row r="102">
@@ -4566,7 +4566,11 @@
           <t>Impairment of GST receivable</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -4644,7 +4648,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>-0.003583</v>
       </c>
@@ -5050,7 +5058,11 @@
           <t>Proceeds from share issuance (Note 6)</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="n">
         <v>0.465</v>
       </c>
@@ -5439,7 +5451,11 @@
           <t>Proceeds from share issuance (Note 6)</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E48" s="5" t="n">
         <v>0.465</v>
       </c>
